--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260901.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>366,786,302</t>
+          <t>70,324,050</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>70,324,050</t>
+          <t>366,786,302</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>305,097,615</t>
+          <t>72,018,440</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,018,440</t>
+          <t>305,097,615</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>261,154,115</t>
+          <t>17,752,768</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,752,768</t>
+          <t>261,154,115</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4,990,119</t>
+          <t>25,473,133</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,473,133</t>
+          <t>4,990,119</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
